--- a/data/Sourcing_Channels_Master.xlsx
+++ b/data/Sourcing_Channels_Master.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Praveen SN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://labournetservices-my.sharepoint.com/personal/praveen_sn_sambhavfoundation_org/Documents/Desktop/Totay/MIS_updated/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{CFE85BF2-FAD3-4A37-82C7-3937416E44E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -308,7 +308,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
